--- a/reports/devops-juniors-israel-2026-W33.xlsx
+++ b/reports/devops-juniors-israel-2026-W33.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="362">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-10T07:59:53</t>
+    <t xml:space="preserve">2026-08-11T07:22:57</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -202,798 +202,756 @@
     <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4443763825</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4452408106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Release Engineering Intern (Part-Time, 80%, One-year temporary position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8069193?gh_jid=8069193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waterfall Security Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-position-at-waterfall-security-solutions-4444878648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4451564107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peak Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, GCP, Cloud (any), Terraform/IaC, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-administrator-at-peak-innovation-4450276163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4442889333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">etoro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations Engineer I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innovid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-engineer-i-at-innovid-4443857656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-unilink-ltd-4446581282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator for Computing Qual (testing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-for-computing-qual-testing-at-applied-materials-israel-4449806027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGILINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Networking, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-agilina-4448561239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QuantHealth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-quanthealth-4444080917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZyG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Git, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-zyg-4441776623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innoviz Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spinomenal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seemplicity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-at-seemplicity-4445609263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - 2107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-2107-at-tsg-4451506512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4442592331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician - Modiin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-modiin-at-nebius-4437655752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helpdesk Specialist טכנאי/ת תמיכה טכנית</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAT Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiryat Gat, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/helpdesk-specialist-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-at-tat-technologies-ltd-4441048130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qb Systems ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-support-engineer-at-qb-systems-ltd-4451539027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magal Security Systems (India) Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magal, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Databases, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-technician-at-magal-security-systems-india-ltd-4442431214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23343 - IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualitest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/23343-it-support-specialist-at-qualitest-4447935579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">איש/אשת תמיכה טכנית ו -Helpdesk 2+בפתח תקווה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arad Tech - Technology, Engineering &amp; AI Recruitment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-%D7%95-helpdesk-2%2B%D7%91%D7%A4%D7%AA%D7%97-%D7%AA%D7%A7%D7%95%D7%95%D7%94-at-arad-tech-technology-engineering-ai-recruitment-4440622529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lab Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lab-support-engineer-at-harmonic-4448547160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-technician-at-energean-4443137036</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-23</t>
   </si>
   <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Release Engineering Intern (Part-Time, 80%, One-year temporary position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8069193?gh_jid=8069193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waterfall Security Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-position-at-waterfall-security-solutions-4444878648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer 24246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-24246-at-comblack-4450246628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peak Innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, GCP, Cloud (any), Terraform/IaC, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-administrator-at-peak-innovation-4450276163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4442889333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, CI/CD, Virtualization, Active Directory, Windows Server, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-experis-israel-4437265103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camtek</t>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4449365989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airobotics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-airobotics-4439190133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reline IT Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-reline-it-solutions-4447384198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-confidential-4444582152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integress, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-integress-inc-4449148474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budapest, Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-extreme-4443366080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Field Operations Technician (IT Support)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Milestone Technologies, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-field-operations-technician-it-support-at-milestone-technologies-inc-4434855297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4446732076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SISL Global</t>
   </si>
   <si>
     <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-support-engineer-at-sisl-global-4440963700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field IT Technician (36179)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-technician-36179-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4451516191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RealPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CYMOTIVE Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-cymotive-technologies-4445985696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Support Specialist (37157)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-specialist-37157-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4451513171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer (Tier 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HCLTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-tier-2-at-hcltech-4445746731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-02</t>
   </si>
   <si>
-    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator &amp; IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inManage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">etoro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations Engineer I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innovid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-engineer-i-at-innovid-4443857656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-unilink-ltd-4446581282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3 Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l3-support-engineer-at-nebius-4437652850</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGILINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Networking, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-agilina-4448561239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QuantHealth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-quanthealth-4444080917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global Service Desk Representative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4442335619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZyG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Git, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-zyg-4441776623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innoviz Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spinomenal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seemplicity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-at-seemplicity-4445609263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4442592331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Modiin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-modiin-at-nebius-4437655752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helpdesk Specialist טכנאי/ת תמיכה טכנית</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAT Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiryat Gat, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/helpdesk-specialist-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-at-tat-technologies-ltd-4441048130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-navina-4397936369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Field IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magal Security Systems (India) Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magal, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Databases, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-technician-at-magal-security-systems-india-ltd-4442431214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23343 - IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualitest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/23343-it-support-specialist-at-qualitest-4447935579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">איש/אשת תמיכה טכנית ו -Helpdesk 2+בפתח תקווה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arad Tech - Technology, Engineering &amp; AI Recruitment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-%D7%95-helpdesk-2%2B%D7%91%D7%A4%D7%AA%D7%97-%D7%AA%D7%A7%D7%95%D7%95%D7%94-at-arad-tech-technology-engineering-ai-recruitment-4440622529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lab Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lab-support-engineer-at-harmonic-4448547160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Energean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-technician-at-energean-4443137036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4449365989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airobotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-airobotics-4439190133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reline IT Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-reline-it-solutions-4447384198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-confidential-4444582152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integress, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-integress-inc-4449148474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ForSight Robotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-at-forsight-robotics-4438498013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budapest, Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-extreme-4443366080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Veridis Environment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-veridis-environment-4448755673</t>
+    <t xml:space="preserve">טכנאי/ת Help desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givat Shmuel, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4448140764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meitar | Law Offices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4450505697</t>
   </si>
   <si>
     <t xml:space="preserve">2026-08-09</t>
   </si>
   <si>
-    <t xml:space="preserve">Technical Field Operations Technician (IT Support)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Milestone Technologies, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-field-operations-technician-it-support-at-milestone-technologies-inc-4434855297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gravity Forms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Git, Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-gravity-forms-4450978605</t>
+    <t xml:space="preserve">Log-On Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-log-on-software-4449514114</t>
   </si>
   <si>
     <t xml:space="preserve">2026-08-10</t>
   </si>
   <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4446732076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SISL Global</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-support-engineer-at-sisl-global-4440963700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RealPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CYMOTIVE Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-cymotive-technologies-4445985696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Engineer (Tier 2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HCLTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-tier-2-at-hcltech-4445746731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">טכנאי/ת Help desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givat Shmuel, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4448140764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meitar | Law Offices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4450505697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log-On Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-log-on-software-4449514114</t>
-  </si>
-  <si>
     <t xml:space="preserve">IT Support Technician</t>
   </si>
   <si>
@@ -1018,15 +976,6 @@
     <t xml:space="preserve">2026-07-13</t>
   </si>
   <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M.D. Mechanical Devices Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-m-d-mechanical-devices-ltd-4444118425</t>
-  </si>
-  <si>
     <t xml:space="preserve">Working Student, Legal (German)</t>
   </si>
   <si>
@@ -1066,27 +1015,36 @@
     <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
   </si>
   <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
     <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
     <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
+    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
+  </si>
+  <si>
     <t xml:space="preserve">CI/CD</t>
   </si>
   <si>
@@ -1097,15 +1055,6 @@
   </si>
   <si>
     <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
     <t xml:space="preserve">Docker</t>
@@ -1275,7 +1224,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">
@@ -1283,7 +1232,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -1291,7 +1240,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -1299,7 +1248,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>618</v>
+        <v>625</v>
       </c>
     </row>
     <row r="10">
@@ -1381,7 +1330,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22">
@@ -1423,7 +1372,7 @@
         <v>30</v>
       </c>
       <c r="B27" s="3">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="28">
@@ -1714,13 +1663,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>83</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>26</v>
@@ -1729,16 +1678,16 @@
         <v>88</v>
       </c>
       <c r="G9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="J9" s="3" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10">
@@ -1746,13 +1695,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>26</v>
@@ -1761,16 +1710,16 @@
         <v>88</v>
       </c>
       <c r="G10" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="J10" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="11">
@@ -1778,13 +1727,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>27</v>
@@ -1793,16 +1742,16 @@
         <v>83</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="12">
@@ -1810,10 +1759,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>98</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>66</v>
@@ -1825,13 +1774,13 @@
         <v>80</v>
       </c>
       <c r="G12" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>100</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>75</v>
@@ -1842,31 +1791,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F13" s="3">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="G13" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="J13" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="14">
@@ -1874,25 +1823,25 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F14" s="3">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>107</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>108</v>
@@ -1912,25 +1861,25 @@
         <v>111</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>112</v>
+        <v>66</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F15" s="3">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G15" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -1938,31 +1887,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="E16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="3">
+        <v>51</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F16" s="3">
-        <v>52</v>
-      </c>
-      <c r="G16" s="3" t="s">
+      <c r="H16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="H16" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>120</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="17">
@@ -1970,19 +1919,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F17" s="3">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>124</v>
@@ -2008,25 +1957,25 @@
         <v>128</v>
       </c>
       <c r="D18" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F18" s="3">
+        <v>48</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" s="3">
-        <v>51</v>
-      </c>
-      <c r="G18" s="3" t="s">
+      <c r="H18" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I18" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>131</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="19">
@@ -2034,13 +1983,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="3" t="s">
         <v>134</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>135</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>26</v>
@@ -2049,16 +1998,16 @@
         <v>48</v>
       </c>
       <c r="G19" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="H19" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>137</v>
-      </c>
       <c r="J19" s="3" t="s">
-        <v>138</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20">
@@ -2066,31 +2015,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F20" s="3">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="G20" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>141</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="21">
@@ -2098,31 +2047,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>144</v>
+        <v>115</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>146</v>
+        <v>60</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F21" s="3">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>105</v>
+        <v>145</v>
       </c>
     </row>
     <row r="22">
@@ -2130,31 +2079,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="3">
+        <v>34</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="J22" s="3" t="s">
         <v>149</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F22" s="3">
-        <v>40</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="23">
@@ -2162,31 +2111,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F23" s="3">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="24">
@@ -2194,31 +2143,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>66</v>
+        <v>117</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>162</v>
+        <v>109</v>
       </c>
     </row>
     <row r="25">
@@ -2226,10 +2175,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>127</v>
+        <v>158</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>66</v>
@@ -2238,19 +2187,19 @@
         <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>166</v>
+        <v>131</v>
       </c>
     </row>
     <row r="26">
@@ -2258,31 +2207,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>78</v>
+        <v>164</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F26" s="3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>171</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -2335,7 +2284,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>34</v>
@@ -2350,22 +2299,22 @@
         <v>37</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>39</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>41</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2">
@@ -2388,7 +2337,7 @@
         <v>45</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>30</v>
@@ -2400,7 +2349,7 @@
         <v>47</v>
       </c>
       <c r="K2" s="3">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3">
@@ -2423,7 +2372,7 @@
         <v>50</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>30</v>
@@ -2435,7 +2384,7 @@
         <v>52</v>
       </c>
       <c r="K3" s="3">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4">
@@ -2458,7 +2407,7 @@
         <v>55</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>30</v>
@@ -2470,7 +2419,7 @@
         <v>57</v>
       </c>
       <c r="K4" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -2493,7 +2442,7 @@
         <v>61</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>30</v>
@@ -2505,7 +2454,7 @@
         <v>63</v>
       </c>
       <c r="K5" s="3">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -2528,7 +2477,7 @@
         <v>67</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>30</v>
@@ -2540,7 +2489,7 @@
         <v>69</v>
       </c>
       <c r="K6" s="3">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">
@@ -2563,7 +2512,7 @@
         <v>73</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
@@ -2575,7 +2524,7 @@
         <v>75</v>
       </c>
       <c r="K7" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -2598,7 +2547,7 @@
         <v>79</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>30</v>
@@ -2610,18 +2559,18 @@
         <v>57</v>
       </c>
       <c r="K8" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>83</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>26</v>
@@ -2630,33 +2579,33 @@
         <v>88</v>
       </c>
       <c r="F9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="J9" s="3" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="K9" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>26</v>
@@ -2665,33 +2614,33 @@
         <v>88</v>
       </c>
       <c r="F10" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="J10" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>86</v>
-      </c>
       <c r="K10" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>27</v>
@@ -2700,30 +2649,30 @@
         <v>83</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="J11" s="3" t="s">
-        <v>96</v>
-      </c>
       <c r="K11" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>98</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>66</v>
@@ -2735,83 +2684,83 @@
         <v>80</v>
       </c>
       <c r="F12" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>100</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>75</v>
       </c>
       <c r="K12" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E13" s="3">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="F13" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="J13" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="K13" s="3">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E14" s="3">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>107</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>108</v>
@@ -2820,7 +2769,7 @@
         <v>109</v>
       </c>
       <c r="K14" s="3">
-        <v>19</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2831,89 +2780,89 @@
         <v>111</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>112</v>
+        <v>66</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E15" s="3">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F15" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>115</v>
-      </c>
       <c r="K15" s="3">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="3">
+        <v>51</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="3">
-        <v>52</v>
-      </c>
-      <c r="F16" s="3" t="s">
+      <c r="G16" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="J16" s="3" t="s">
-        <v>121</v>
-      </c>
       <c r="K16" s="3">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="C17" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E17" s="3">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>124</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>30</v>
@@ -2925,7 +2874,7 @@
         <v>126</v>
       </c>
       <c r="K17" s="3">
-        <v>41</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
@@ -2936,42 +2885,42 @@
         <v>128</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" s="3">
+        <v>48</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="3">
-        <v>51</v>
-      </c>
-      <c r="F18" s="3" t="s">
+      <c r="G18" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I18" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="K18" s="3">
-        <v>40</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="C19" s="3" t="s">
         <v>134</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>135</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>26</v>
@@ -2980,205 +2929,205 @@
         <v>48</v>
       </c>
       <c r="F19" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>137</v>
-      </c>
       <c r="J19" s="3" t="s">
-        <v>138</v>
+        <v>63</v>
       </c>
       <c r="K19" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E20" s="3">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="F20" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>143</v>
-      </c>
       <c r="K20" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>144</v>
+        <v>115</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>146</v>
+        <v>60</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E21" s="3">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="K21" s="3">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" s="3">
+        <v>34</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="J22" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E22" s="3">
-        <v>40</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>153</v>
-      </c>
       <c r="K22" s="3">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E23" s="3">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="K23" s="3">
-        <v>17</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>66</v>
+        <v>117</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>162</v>
+        <v>109</v>
       </c>
       <c r="K24" s="3">
-        <v>15</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>127</v>
+        <v>158</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>66</v>
@@ -3187,211 +3136,211 @@
         <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>166</v>
+        <v>131</v>
       </c>
       <c r="K25" s="3">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>78</v>
+        <v>164</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E26" s="3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>171</v>
+        <v>63</v>
       </c>
       <c r="K26" s="3">
-        <v>71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>178</v>
+        <v>59</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>129</v>
+        <v>66</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E27" s="3">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>121</v>
+        <v>176</v>
       </c>
       <c r="K27" s="3">
-        <v>47</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E28" s="3">
+        <v>24</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J28" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E28" s="3">
-        <v>30</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>143</v>
-      </c>
       <c r="K28" s="3">
-        <v>10</v>
+        <v>88</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>59</v>
+        <v>183</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>66</v>
+        <v>184</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E29" s="3">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F29" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I29" s="3" t="s">
+      <c r="J29" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>188</v>
-      </c>
       <c r="K29" s="3">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E30" s="3">
+        <v>23</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I30" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="J30" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E30" s="3">
-        <v>24</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>193</v>
-      </c>
       <c r="K30" s="3">
-        <v>87</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>146</v>
+        <v>193</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>25</v>
@@ -3400,33 +3349,33 @@
         <v>23</v>
       </c>
       <c r="F31" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I31" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>196</v>
-      </c>
       <c r="J31" s="3" t="s">
-        <v>197</v>
+        <v>145</v>
       </c>
       <c r="K31" s="3">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>145</v>
+        <v>197</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>146</v>
+        <v>60</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>25</v>
@@ -3435,10 +3384,10 @@
         <v>23</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>30</v>
@@ -3447,10 +3396,10 @@
         <v>199</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>105</v>
+        <v>63</v>
       </c>
       <c r="K32" s="3">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -3467,25 +3416,25 @@
         <v>25</v>
       </c>
       <c r="E33" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>203</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>204</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="K33" s="3">
-        <v>17</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34">
@@ -3496,42 +3445,42 @@
         <v>206</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>135</v>
+        <v>207</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E34" s="3">
+        <v>20</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="K34" s="3">
         <v>23</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="K34" s="3">
-        <v>82</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>25</v>
@@ -3540,33 +3489,33 @@
         <v>20</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>193</v>
+        <v>126</v>
       </c>
       <c r="K35" s="3">
-        <v>87</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>25</v>
@@ -3575,103 +3524,103 @@
         <v>20</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K36" s="3">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E37" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>138</v>
+        <v>227</v>
       </c>
       <c r="K37" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E38" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="K38" s="3">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>233</v>
+        <v>178</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>234</v>
+        <v>82</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>25</v>
@@ -3683,7 +3632,7 @@
         <v>235</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>30</v>
@@ -3692,21 +3641,21 @@
         <v>236</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="K39" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>239</v>
-      </c>
       <c r="C40" s="3" t="s">
-        <v>240</v>
+        <v>218</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>25</v>
@@ -3715,33 +3664,33 @@
         <v>17</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>63</v>
+        <v>240</v>
       </c>
       <c r="K40" s="3">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>190</v>
+        <v>241</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>83</v>
+        <v>242</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>25</v>
@@ -3750,33 +3699,33 @@
         <v>17</v>
       </c>
       <c r="F41" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I41" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>245</v>
-      </c>
       <c r="J41" s="3" t="s">
-        <v>237</v>
+        <v>141</v>
       </c>
       <c r="K41" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="C42" s="3" t="s">
         <v>247</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>228</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>25</v>
@@ -3785,10 +3734,10 @@
         <v>17</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>30</v>
@@ -3797,21 +3746,21 @@
         <v>248</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>249</v>
+        <v>131</v>
       </c>
       <c r="K42" s="3">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>243</v>
+        <v>115</v>
       </c>
       <c r="B43" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>250</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>251</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>25</v>
@@ -3820,80 +3769,80 @@
         <v>17</v>
       </c>
       <c r="F43" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I43" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>253</v>
-      </c>
       <c r="J43" s="3" t="s">
-        <v>153</v>
+        <v>89</v>
       </c>
       <c r="K43" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="D44" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E44" s="3">
+        <v>13</v>
+      </c>
+      <c r="F44" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="G44" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I44" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E44" s="3">
-        <v>17</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I44" s="3" t="s">
+      <c r="J44" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>143</v>
-      </c>
       <c r="K44" s="3">
-        <v>10</v>
+        <v>34</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>127</v>
+        <v>258</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>259</v>
+        <v>218</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E45" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>260</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>30</v>
@@ -3902,10 +3851,10 @@
         <v>261</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="K45" s="3">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46">
@@ -3916,89 +3865,89 @@
         <v>263</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>234</v>
+        <v>66</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E46" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>235</v>
+        <v>264</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="K46" s="3">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>71</v>
+        <v>267</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E47" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>269</v>
+        <v>52</v>
       </c>
       <c r="K47" s="3">
-        <v>33</v>
+        <v>79</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>271</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>228</v>
+        <v>66</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E48" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>272</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>30</v>
@@ -4007,45 +3956,45 @@
         <v>273</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>109</v>
+        <v>274</v>
       </c>
       <c r="K48" s="3">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>167</v>
+        <v>196</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>44</v>
+        <v>276</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E49" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>277</v>
+        <v>221</v>
       </c>
       <c r="K49" s="3">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="50">
@@ -4056,322 +4005,322 @@
         <v>279</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E50" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F50" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I50" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="G50" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>281</v>
-      </c>
       <c r="J50" s="3" t="s">
-        <v>237</v>
+        <v>63</v>
       </c>
       <c r="K50" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>282</v>
+        <v>115</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>284</v>
+        <v>66</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E51" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>287</v>
+        <v>52</v>
       </c>
       <c r="K51" s="3">
-        <v>0</v>
+        <v>79</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>288</v>
+        <v>234</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>290</v>
+        <v>66</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E52" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>52</v>
+        <v>131</v>
       </c>
       <c r="K52" s="3">
-        <v>78</v>
+        <v>11</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>270</v>
+        <v>287</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E53" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>296</v>
+        <v>63</v>
       </c>
       <c r="K53" s="3">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E54" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>231</v>
+        <v>293</v>
       </c>
       <c r="K54" s="3">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>127</v>
+        <v>294</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>300</v>
+        <v>91</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E55" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>52</v>
+        <v>297</v>
       </c>
       <c r="K55" s="3">
-        <v>78</v>
+        <v>40</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>243</v>
+        <v>298</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>66</v>
+        <v>300</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E56" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="K56" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>60</v>
+        <v>123</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E57" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="K57" s="3">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E58" s="3">
+        <v>3</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="J58" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="B58" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E58" s="3">
-        <v>4</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>115</v>
-      </c>
       <c r="K58" s="3">
-        <v>39</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>316</v>
+        <v>184</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>25</v>
@@ -4380,33 +4329,33 @@
         <v>3</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>138</v>
+        <v>190</v>
       </c>
       <c r="K59" s="3">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>25</v>
@@ -4415,199 +4364,59 @@
         <v>3</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>277</v>
+        <v>319</v>
       </c>
       <c r="K60" s="3">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>270</v>
+        <v>320</v>
       </c>
       <c r="B61" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3"/>
+      <c r="G61" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I61" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="C61" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E61" s="3">
-        <v>3</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I61" s="3" t="s">
-        <v>325</v>
-      </c>
       <c r="J61" s="3" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="K61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E62" s="3">
-        <v>3</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="K62" s="3">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E63" s="3">
-        <v>3</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H63" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I63" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="J63" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="K63" s="3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E64" s="3">
-        <v>3</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="G64" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H64" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I64" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="J64" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="K64" s="3">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E65" s="3">
-        <v>0</v>
-      </c>
-      <c r="F65" s="3"/>
-      <c r="G65" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H65" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I65" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="J65" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="K65" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K65"/>
+  <autoFilter ref="A1:K61"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -4669,10 +4478,6 @@
     <hyperlink ref="I59" r:id="rId58"/>
     <hyperlink ref="I60" r:id="rId59"/>
     <hyperlink ref="I61" r:id="rId60"/>
-    <hyperlink ref="I62" r:id="rId61"/>
-    <hyperlink ref="I63" r:id="rId62"/>
-    <hyperlink ref="I64" r:id="rId63"/>
-    <hyperlink ref="I65" r:id="rId64"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4680,11 +4485,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="1" max="1" width="51" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
@@ -4703,10 +4508,10 @@
         <v>37</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>41</v>
@@ -4714,55 +4519,175 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>282</v>
+        <v>58</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>283</v>
+        <v>59</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" s="3">
-        <v>13</v>
+        <v>100</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>285</v>
+        <v>61</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>286</v>
+        <v>62</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>287</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>270</v>
+        <v>64</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>323</v>
+        <v>81</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="3">
+        <v>88</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="3">
+        <v>48</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="3">
+        <v>28</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="3">
-        <v>3</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="G3" s="3" t="s">
+      <c r="D6" s="3">
+        <v>23</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="3">
+        <v>10</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
         <v>287</v>
       </c>
+      <c r="B8" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="3">
+        <v>6</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>63</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G8"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
+    <hyperlink ref="F4" r:id="rId3"/>
+    <hyperlink ref="F5" r:id="rId4"/>
+    <hyperlink ref="F6" r:id="rId5"/>
+    <hyperlink ref="F7" r:id="rId6"/>
+    <hyperlink ref="F8" r:id="rId7"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4777,178 +4702,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>341</v>
+        <v>324</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>342</v>
+        <v>325</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="B2" s="3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>321</v>
+        <v>305</v>
       </c>
       <c r="B3" s="3">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>345</v>
+        <v>328</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>346</v>
+        <v>329</v>
       </c>
       <c r="B4" s="3">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>347</v>
+        <v>330</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="B5" s="3">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>349</v>
+        <v>332</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>350</v>
+        <v>295</v>
       </c>
       <c r="B6" s="3">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>351</v>
+        <v>333</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>267</v>
+        <v>334</v>
       </c>
       <c r="B7" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>352</v>
+        <v>335</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B8" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>353</v>
+        <v>336</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>324</v>
+        <v>255</v>
       </c>
       <c r="B9" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>354</v>
+        <v>337</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>355</v>
+        <v>338</v>
       </c>
       <c r="B10" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>356</v>
+        <v>339</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>357</v>
+        <v>301</v>
       </c>
       <c r="B11" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>358</v>
+        <v>340</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>359</v>
+        <v>341</v>
       </c>
       <c r="B12" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>360</v>
+        <v>342</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>317</v>
+        <v>343</v>
       </c>
       <c r="B13" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>361</v>
+        <v>344</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>362</v>
+        <v>345</v>
       </c>
       <c r="B14" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>364</v>
+        <v>347</v>
       </c>
       <c r="B15" s="3">
         <v>9</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>365</v>
+        <v>348</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>366</v>
+        <v>349</v>
       </c>
       <c r="B16" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>367</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>
@@ -4968,10 +4893,10 @@
         <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>368</v>
+        <v>351</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>369</v>
+        <v>352</v>
       </c>
     </row>
     <row r="2">
@@ -4979,10 +4904,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>370</v>
+        <v>353</v>
       </c>
     </row>
     <row r="3">
@@ -4993,7 +4918,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>371</v>
+        <v>354</v>
       </c>
     </row>
     <row r="4">
@@ -5004,7 +4929,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>372</v>
+        <v>355</v>
       </c>
     </row>
     <row r="5">
@@ -5015,7 +4940,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>373</v>
+        <v>356</v>
       </c>
     </row>
   </sheetData>
@@ -5036,13 +4961,13 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>374</v>
+        <v>357</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>375</v>
+        <v>358</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>376</v>
+        <v>359</v>
       </c>
     </row>
     <row r="2">
@@ -5053,7 +4978,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>377</v>
+        <v>360</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -5062,22 +4987,22 @@
         <v>30</v>
       </c>
       <c r="B3" s="3">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>377</v>
+        <v>360</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>378</v>
+        <v>361</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>377</v>
+        <v>360</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W33.xlsx
+++ b/reports/devops-juniors-israel-2026-W33.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="341">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-11T07:22:57</t>
+    <t xml:space="preserve">2026-08-12T07:46:38</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -271,21 +271,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4451564107</t>
   </si>
   <si>
-    <t xml:space="preserve">IT System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peak Innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, GCP, Cloud (any), Terraform/IaC, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-administrator-at-peak-innovation-4450276163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-07</t>
-  </si>
-  <si>
     <t xml:space="preserve">Devops Student</t>
   </si>
   <si>
@@ -328,180 +313,171 @@
     <t xml:space="preserve">2026-07-22</t>
   </si>
   <si>
-    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">etoro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations Engineer I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innovid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-engineer-i-at-innovid-4443857656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4451682760</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-unilink-ltd-4446581282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator for Computing Qual (testing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-for-computing-qual-testing-at-applied-materials-israel-4449806027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4377864560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGILINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Networking, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-agilina-4448561239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QuantHealth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-quanthealth-4444080917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZyG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Git, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-zyg-4441776623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spinomenal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-24</t>
   </si>
   <si>
-    <t xml:space="preserve">System Administrator &amp; IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inManage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">etoro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations Engineer I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innovid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-engineer-i-at-innovid-4443857656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-unilink-ltd-4446581282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator for Computing Qual (testing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-for-computing-qual-testing-at-applied-materials-israel-4449806027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGILINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Networking, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-agilina-4448561239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QuantHealth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-quanthealth-4444080917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZyG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Git, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-zyg-4441776623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innoviz Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spinomenal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seemplicity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-at-seemplicity-4445609263</t>
-  </si>
-  <si>
     <t xml:space="preserve">System Administrator - 2107</t>
   </si>
   <si>
@@ -517,6 +493,33 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-2107-at-tsg-4451506512</t>
   </si>
   <si>
+    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4442592331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-15</t>
+  </si>
+  <si>
     <t xml:space="preserve">Title</t>
   </si>
   <si>
@@ -535,33 +538,6 @@
     <t xml:space="preserve">no</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4442592331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-15</t>
-  </si>
-  <si>
     <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
   </si>
   <si>
@@ -604,214 +580,202 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/helpdesk-specialist-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-at-tat-technologies-ltd-4441048130</t>
   </si>
   <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magal Security Systems (India) Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magal, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Databases, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-technician-at-magal-security-systems-india-ltd-4442431214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23343 - IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualitest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/23343-it-support-specialist-at-qualitest-4447935579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">איש/אשת תמיכה טכנית ו -Helpdesk 2+בפתח תקווה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arad Tech - Technology, Engineering &amp; AI Recruitment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-%D7%95-helpdesk-2%2B%D7%91%D7%A4%D7%AA%D7%97-%D7%AA%D7%A7%D7%95%D7%95%D7%94-at-arad-tech-technology-engineering-ai-recruitment-4440622529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lab Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lab-support-engineer-at-harmonic-4448547160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-technician-at-energean-4443137036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4449365989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airobotics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-airobotics-4439190133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reline IT Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-reline-it-solutions-4447384198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-confidential-4444582152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budapest, Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-extreme-4443366080</t>
+  </si>
+  <si>
     <t xml:space="preserve">Information Technology Support Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">qb Systems ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-support-engineer-at-qb-systems-ltd-4451539027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Field IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magal Security Systems (India) Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magal, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Databases, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-technician-at-magal-security-systems-india-ltd-4442431214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23343 - IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualitest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/23343-it-support-specialist-at-qualitest-4447935579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">איש/אשת תמיכה טכנית ו -Helpdesk 2+בפתח תקווה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arad Tech - Technology, Engineering &amp; AI Recruitment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-%D7%95-helpdesk-2%2B%D7%91%D7%A4%D7%AA%D7%97-%D7%AA%D7%A7%D7%95%D7%95%D7%94-at-arad-tech-technology-engineering-ai-recruitment-4440622529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lab Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lab-support-engineer-at-harmonic-4448547160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Energean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-technician-at-energean-4443137036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4449365989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airobotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-airobotics-4439190133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reline IT Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-reline-it-solutions-4447384198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-confidential-4444582152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integress, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-integress-inc-4449148474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budapest, Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-extreme-4443366080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Field Operations Technician (IT Support)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Milestone Technologies, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-field-operations-technician-it-support-at-milestone-technologies-inc-4434855297</t>
+    <t xml:space="preserve">SISL Global</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-support-engineer-at-sisl-global-4440963700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4446743008</t>
   </si>
   <si>
     <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
@@ -823,15 +787,9 @@
     <t xml:space="preserve">Estonia</t>
   </si>
   <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
   </si>
   <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
     <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
   </si>
   <si>
@@ -841,15 +799,6 @@
     <t xml:space="preserve">2026-07-30</t>
   </si>
   <si>
-    <t xml:space="preserve">SISL Global</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-support-engineer-at-sisl-global-4440963700</t>
-  </si>
-  <si>
     <t xml:space="preserve">Field IT Technician (36179)</t>
   </si>
   <si>
@@ -868,126 +817,114 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
   </si>
   <si>
-    <t xml:space="preserve">CYMOTIVE Technologies</t>
+    <t xml:space="preserve">Help Desk Support Specialist (37157)</t>
   </si>
   <si>
     <t xml:space="preserve">Active Directory, Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-cymotive-technologies-4445985696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Support Specialist (37157)</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-specialist-37157-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4451513171</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Support Engineer (Tier 2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HCLTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-tier-2-at-hcltech-4445746731</t>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">טכנאי/ת Help desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givat Shmuel, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4448140764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meitar | Law Offices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4450505697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-On Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-log-on-software-4449514114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-flex-4436841213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phibro Middle East &amp; Europe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-specialist-at-phibro-middle-east-europe-4439142494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M.D. Mechanical Devices Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-m-d-mechanical-devices-ltd-4444118425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Working Student, Legal (German)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Via</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berlin, Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-29</t>
   </si>
   <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">טכנאי/ת Help desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givat Shmuel, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4448140764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meitar | Law Offices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4450505697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log-On Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-log-on-software-4449514114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-flex-4436841213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phibro Middle East &amp; Europe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-specialist-at-phibro-middle-east-europe-4439142494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Working Student, Legal (German)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Via</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berlin, Germany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
-  </si>
-  <si>
     <t xml:space="preserve">Skill</t>
   </si>
   <si>
@@ -1009,31 +946,37 @@
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
     <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
   </si>
   <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
     <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
   </si>
   <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
   </si>
   <si>
     <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
@@ -1043,12 +986,6 @@
   </si>
   <si>
     <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
   </si>
   <si>
     <t xml:space="preserve">Azure</t>
@@ -1224,7 +1161,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
@@ -1232,7 +1169,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -1240,7 +1177,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -1248,7 +1185,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="10">
@@ -1330,7 +1267,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22">
@@ -1372,7 +1309,7 @@
         <v>30</v>
       </c>
       <c r="B27" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28">
@@ -1392,7 +1329,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="32" customWidth="1"/>
+    <col min="3" max="3" width="37" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -1701,25 +1638,25 @@
         <v>86</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F10" s="3">
+        <v>83</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="H10" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11">
@@ -1727,31 +1664,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F11" s="3">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>93</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>94</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12">
@@ -1759,31 +1696,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F12" s="3">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="G12" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="13">
@@ -1791,25 +1728,25 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="D13" s="3" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F13" s="3">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>101</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>102</v>
@@ -1832,10 +1769,10 @@
         <v>106</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F14" s="3">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>107</v>
@@ -1861,25 +1798,25 @@
         <v>111</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>66</v>
+        <v>112</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F15" s="3">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -1887,31 +1824,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F16" s="3">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17">
@@ -1919,13 +1856,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>122</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>123</v>
+        <v>60</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>26</v>
@@ -1934,16 +1871,16 @@
         <v>48</v>
       </c>
       <c r="G17" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="18">
@@ -1951,13 +1888,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>128</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>26</v>
@@ -1975,7 +1912,7 @@
         <v>130</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19">
@@ -1983,31 +1920,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" s="3">
+        <v>47</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="H19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F19" s="3">
-        <v>48</v>
-      </c>
-      <c r="G19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>135</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="20">
@@ -2015,13 +1952,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>138</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>26</v>
@@ -2030,16 +1967,16 @@
         <v>40</v>
       </c>
       <c r="G20" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="21">
@@ -2047,10 +1984,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>60</v>
@@ -2062,16 +1999,16 @@
         <v>40</v>
       </c>
       <c r="G21" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="22">
@@ -2079,10 +2016,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>66</v>
@@ -2094,16 +2031,16 @@
         <v>34</v>
       </c>
       <c r="G22" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>148</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="23">
@@ -2111,13 +2048,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>151</v>
-      </c>
       <c r="D23" s="3" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>25</v>
@@ -2126,16 +2063,16 @@
         <v>30</v>
       </c>
       <c r="G23" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>153</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="24">
@@ -2143,31 +2080,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>155</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>117</v>
+        <v>156</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F24" s="3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>109</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25">
@@ -2175,10 +2112,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>159</v>
+        <v>59</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>66</v>
@@ -2187,7 +2124,7 @@
         <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>160</v>
@@ -2199,7 +2136,7 @@
         <v>161</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
     </row>
     <row r="26">
@@ -2207,19 +2144,19 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>164</v>
+        <v>82</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F26" s="3">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>165</v>
@@ -2231,7 +2168,7 @@
         <v>166</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>63</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -2284,7 +2221,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>34</v>
@@ -2299,22 +2236,22 @@
         <v>37</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>39</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>41</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2">
@@ -2337,7 +2274,7 @@
         <v>45</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>30</v>
@@ -2349,7 +2286,7 @@
         <v>47</v>
       </c>
       <c r="K2" s="3">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3">
@@ -2372,7 +2309,7 @@
         <v>50</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>30</v>
@@ -2384,7 +2321,7 @@
         <v>52</v>
       </c>
       <c r="K3" s="3">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4">
@@ -2407,7 +2344,7 @@
         <v>55</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>30</v>
@@ -2419,7 +2356,7 @@
         <v>57</v>
       </c>
       <c r="K4" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -2442,7 +2379,7 @@
         <v>61</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>30</v>
@@ -2454,7 +2391,7 @@
         <v>63</v>
       </c>
       <c r="K5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -2477,7 +2414,7 @@
         <v>67</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>30</v>
@@ -2489,7 +2426,7 @@
         <v>69</v>
       </c>
       <c r="K6" s="3">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7">
@@ -2512,7 +2449,7 @@
         <v>73</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
@@ -2524,7 +2461,7 @@
         <v>75</v>
       </c>
       <c r="K7" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -2547,7 +2484,7 @@
         <v>79</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>30</v>
@@ -2559,7 +2496,7 @@
         <v>57</v>
       </c>
       <c r="K8" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -2582,7 +2519,7 @@
         <v>83</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>30</v>
@@ -2594,7 +2531,7 @@
         <v>63</v>
       </c>
       <c r="K9" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -2605,63 +2542,63 @@
         <v>86</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E10" s="3">
+        <v>83</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="G10" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K10" s="3">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E11" s="3">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>93</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>94</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="K11" s="3">
         <v>15</v>
@@ -2669,63 +2606,63 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E12" s="3">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="F12" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>75</v>
-      </c>
       <c r="K12" s="3">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="C13" s="3" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E13" s="3">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>101</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>102</v>
@@ -2734,7 +2671,7 @@
         <v>103</v>
       </c>
       <c r="K13" s="3">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14">
@@ -2748,16 +2685,16 @@
         <v>106</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E14" s="3">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>107</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>30</v>
@@ -2769,7 +2706,7 @@
         <v>109</v>
       </c>
       <c r="K14" s="3">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15">
@@ -2780,77 +2717,77 @@
         <v>111</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>66</v>
+        <v>112</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E15" s="3">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K15" s="3">
-        <v>42</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E16" s="3">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K16" s="3">
-        <v>41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>122</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>123</v>
+        <v>60</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>26</v>
@@ -2859,33 +2796,33 @@
         <v>48</v>
       </c>
       <c r="F17" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>126</v>
-      </c>
       <c r="K17" s="3">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>128</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>26</v>
@@ -2897,7 +2834,7 @@
         <v>129</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>30</v>
@@ -2906,56 +2843,56 @@
         <v>130</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
       <c r="K18" s="3">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="C19" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" s="3">
+        <v>47</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="G19" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E19" s="3">
-        <v>48</v>
-      </c>
-      <c r="F19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>63</v>
-      </c>
       <c r="K19" s="3">
-        <v>0</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>138</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>26</v>
@@ -2964,30 +2901,30 @@
         <v>40</v>
       </c>
       <c r="F20" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>141</v>
-      </c>
       <c r="K20" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>60</v>
@@ -2999,30 +2936,30 @@
         <v>40</v>
       </c>
       <c r="F21" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>145</v>
-      </c>
       <c r="K21" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>66</v>
@@ -3034,33 +2971,33 @@
         <v>34</v>
       </c>
       <c r="F22" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>149</v>
-      </c>
       <c r="K22" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>151</v>
-      </c>
       <c r="C23" s="3" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>25</v>
@@ -3069,65 +3006,65 @@
         <v>30</v>
       </c>
       <c r="F23" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>154</v>
-      </c>
       <c r="K23" s="3">
-        <v>72</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>155</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>117</v>
+        <v>156</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E24" s="3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>109</v>
+        <v>63</v>
       </c>
       <c r="K24" s="3">
-        <v>48</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>159</v>
+        <v>59</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>66</v>
@@ -3136,13 +3073,13 @@
         <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>160</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>30</v>
@@ -3151,33 +3088,33 @@
         <v>161</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="K25" s="3">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>164</v>
+        <v>82</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E26" s="3">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>165</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>30</v>
@@ -3186,91 +3123,91 @@
         <v>166</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>63</v>
+        <v>167</v>
       </c>
       <c r="K26" s="3">
-        <v>0</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>59</v>
+        <v>175</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>66</v>
+        <v>176</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E27" s="3">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="K27" s="3">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E28" s="3">
+        <v>23</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E28" s="3">
-        <v>24</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>179</v>
-      </c>
       <c r="G28" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K28" s="3">
-        <v>88</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>25</v>
@@ -3279,22 +3216,22 @@
         <v>23</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>187</v>
+        <v>144</v>
       </c>
       <c r="K29" s="3">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30">
@@ -3302,115 +3239,115 @@
         <v>188</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E30" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>190</v>
+        <v>167</v>
       </c>
       <c r="K30" s="3">
-        <v>27</v>
+        <v>89</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E31" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>145</v>
+        <v>198</v>
       </c>
       <c r="K31" s="3">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>60</v>
+        <v>201</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E32" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>63</v>
+        <v>115</v>
       </c>
       <c r="K32" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>25</v>
@@ -3419,138 +3356,138 @@
         <v>20</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>181</v>
+        <v>209</v>
       </c>
       <c r="K33" s="3">
-        <v>88</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E34" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="K34" s="3">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E35" s="3">
+        <v>17</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="K35" s="3">
         <v>20</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="K35" s="3">
-        <v>7</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>217</v>
+        <v>164</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>218</v>
+        <v>82</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E36" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="K36" s="3">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>25</v>
@@ -3559,27 +3496,27 @@
         <v>17</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K37" s="3">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>229</v>
@@ -3597,7 +3534,7 @@
         <v>231</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>30</v>
@@ -3606,21 +3543,21 @@
         <v>232</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>233</v>
+        <v>140</v>
       </c>
       <c r="K38" s="3">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>178</v>
-      </c>
       <c r="C39" s="3" t="s">
-        <v>82</v>
+        <v>235</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>25</v>
@@ -3629,10 +3566,10 @@
         <v>17</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>30</v>
@@ -3641,10 +3578,10 @@
         <v>236</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>227</v>
+        <v>125</v>
       </c>
       <c r="K39" s="3">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40">
@@ -3652,255 +3589,255 @@
         <v>237</v>
       </c>
       <c r="B40" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>218</v>
-      </c>
       <c r="D40" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E40" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K40" s="3">
-        <v>28</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>242</v>
+        <v>206</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E41" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>141</v>
+        <v>98</v>
       </c>
       <c r="K41" s="3">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E42" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>131</v>
+        <v>209</v>
       </c>
       <c r="K42" s="3">
-        <v>11</v>
+        <v>27</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>115</v>
+        <v>163</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>250</v>
+        <v>206</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E43" s="3">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>89</v>
+        <v>121</v>
       </c>
       <c r="K43" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>71</v>
+        <v>255</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E44" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>257</v>
+        <v>52</v>
       </c>
       <c r="K44" s="3">
-        <v>34</v>
+        <v>80</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>218</v>
+        <v>66</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E45" s="3">
+        <v>10</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="K45" s="3">
         <v>13</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K45" s="3">
-        <v>20</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>263</v>
-      </c>
       <c r="C46" s="3" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E46" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>227</v>
+        <v>63</v>
       </c>
       <c r="K46" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>266</v>
+        <v>104</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>268</v>
+        <v>66</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>25</v>
@@ -3909,185 +3846,185 @@
         <v>10</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>52</v>
       </c>
       <c r="K47" s="3">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E48" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>274</v>
+        <v>63</v>
       </c>
       <c r="K48" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>196</v>
+        <v>270</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>275</v>
+        <v>86</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>276</v>
+        <v>87</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E49" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F49" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I49" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>277</v>
-      </c>
       <c r="J49" s="3" t="s">
-        <v>221</v>
+        <v>273</v>
       </c>
       <c r="K49" s="3">
-        <v>26</v>
+        <v>41</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>82</v>
+        <v>276</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E50" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>63</v>
+        <v>115</v>
       </c>
       <c r="K50" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>115</v>
+        <v>279</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>66</v>
+        <v>112</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E51" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F51" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I51" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="G51" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I51" s="3" t="s">
+      <c r="J51" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="J51" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="K51" s="3">
-        <v>79</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>284</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>66</v>
+        <v>137</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E52" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>285</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>30</v>
@@ -4096,115 +4033,115 @@
         <v>286</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>131</v>
+        <v>287</v>
       </c>
       <c r="K52" s="3">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E53" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>63</v>
+        <v>182</v>
       </c>
       <c r="K53" s="3">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E54" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="K54" s="3">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>294</v>
+        <v>131</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>91</v>
+        <v>296</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>92</v>
+        <v>218</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E55" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>297</v>
+        <v>260</v>
       </c>
       <c r="K55" s="3">
-        <v>40</v>
+        <v>13</v>
       </c>
     </row>
     <row r="56">
@@ -4218,205 +4155,30 @@
         <v>300</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E56" s="3">
-        <v>3</v>
-      </c>
-      <c r="F56" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I56" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="G56" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H56" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I56" s="3" t="s">
+      <c r="J56" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="J56" s="3" t="s">
-        <v>126</v>
-      </c>
       <c r="K56" s="3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E57" s="3">
-        <v>3</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="K57" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E58" s="3">
-        <v>3</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="K58" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E59" s="3">
-        <v>3</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="K59" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E60" s="3">
-        <v>3</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="K60" s="3">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E61" s="3">
-        <v>0</v>
-      </c>
-      <c r="F61" s="3"/>
-      <c r="G61" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I61" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="J61" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="K61" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K61"/>
+  <autoFilter ref="A1:K56"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -4473,11 +4235,6 @@
     <hyperlink ref="I54" r:id="rId53"/>
     <hyperlink ref="I55" r:id="rId54"/>
     <hyperlink ref="I56" r:id="rId55"/>
-    <hyperlink ref="I57" r:id="rId56"/>
-    <hyperlink ref="I58" r:id="rId57"/>
-    <hyperlink ref="I59" r:id="rId58"/>
-    <hyperlink ref="I60" r:id="rId59"/>
-    <hyperlink ref="I61" r:id="rId60"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4485,9 +4242,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="51" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="37" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -4508,10 +4265,10 @@
         <v>37</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>41</v>
@@ -4519,175 +4276,55 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>59</v>
+        <v>117</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D2" s="3">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>61</v>
+        <v>119</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>63</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>64</v>
+        <v>163</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>81</v>
+        <v>251</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D3" s="3">
-        <v>88</v>
+        <v>12</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>83</v>
+        <v>252</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>84</v>
+        <v>253</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="3">
-        <v>48</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="3">
-        <v>28</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="3">
-        <v>23</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="3">
-        <v>10</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="3">
-        <v>6</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>63</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8"/>
+  <autoFilter ref="A1:G3"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
-    <hyperlink ref="F4" r:id="rId3"/>
-    <hyperlink ref="F5" r:id="rId4"/>
-    <hyperlink ref="F6" r:id="rId5"/>
-    <hyperlink ref="F7" r:id="rId6"/>
-    <hyperlink ref="F8" r:id="rId7"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4702,178 +4339,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>324</v>
+        <v>303</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>325</v>
+        <v>304</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>326</v>
+        <v>305</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>314</v>
+        <v>290</v>
       </c>
       <c r="B2" s="3">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>327</v>
+        <v>306</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>305</v>
+        <v>281</v>
       </c>
       <c r="B3" s="3">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>328</v>
+        <v>307</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>329</v>
+        <v>308</v>
       </c>
       <c r="B4" s="3">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>330</v>
+        <v>309</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>331</v>
+        <v>271</v>
       </c>
       <c r="B5" s="3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>332</v>
+        <v>310</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>295</v>
+        <v>311</v>
       </c>
       <c r="B6" s="3">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>333</v>
+        <v>312</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>334</v>
+        <v>313</v>
       </c>
       <c r="B7" s="3">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>335</v>
+        <v>314</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>309</v>
+        <v>239</v>
       </c>
       <c r="B8" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>336</v>
+        <v>315</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>255</v>
+        <v>316</v>
       </c>
       <c r="B9" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>337</v>
+        <v>317</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>338</v>
+        <v>285</v>
       </c>
       <c r="B10" s="3">
         <v>17</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>339</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="B11" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>341</v>
+        <v>277</v>
       </c>
       <c r="B12" s="3">
         <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>342</v>
+        <v>321</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>343</v>
+        <v>322</v>
       </c>
       <c r="B13" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>344</v>
+        <v>323</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>345</v>
+        <v>324</v>
       </c>
       <c r="B14" s="3">
         <v>10</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>346</v>
+        <v>325</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>347</v>
+        <v>326</v>
       </c>
       <c r="B15" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>348</v>
+        <v>327</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
       <c r="B16" s="3">
         <v>8</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>350</v>
+        <v>329</v>
       </c>
     </row>
   </sheetData>
@@ -4893,10 +4530,10 @@
         <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>351</v>
+        <v>330</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>352</v>
+        <v>331</v>
       </c>
     </row>
     <row r="2">
@@ -4904,10 +4541,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>353</v>
+        <v>332</v>
       </c>
     </row>
     <row r="3">
@@ -4918,7 +4555,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>354</v>
+        <v>333</v>
       </c>
     </row>
     <row r="4">
@@ -4929,7 +4566,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>355</v>
+        <v>334</v>
       </c>
     </row>
     <row r="5">
@@ -4940,7 +4577,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>356</v>
+        <v>335</v>
       </c>
     </row>
   </sheetData>
@@ -4961,13 +4598,13 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>357</v>
+        <v>336</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>358</v>
+        <v>337</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>359</v>
+        <v>338</v>
       </c>
     </row>
     <row r="2">
@@ -4978,7 +4615,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>360</v>
+        <v>339</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -4987,22 +4624,22 @@
         <v>30</v>
       </c>
       <c r="B3" s="3">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>360</v>
+        <v>339</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>361</v>
+        <v>340</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>360</v>
+        <v>339</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W33.xlsx
+++ b/reports/devops-juniors-israel-2026-W33.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="360">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-12T07:46:38</t>
+    <t xml:space="preserve">2026-08-13T07:48:19</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -289,6 +289,21 @@
     <t xml:space="preserve">2026-07-27</t>
   </si>
   <si>
+    <t xml:space="preserve">Test Environment Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-environment-support-engineer-at-abra-4442615924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior Technical Operations Engineer</t>
   </si>
   <si>
@@ -310,9 +325,6 @@
     <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-22</t>
-  </si>
-  <si>
     <t xml:space="preserve">System Administrator &amp; IT</t>
   </si>
   <si>
@@ -346,6 +358,51 @@
     <t xml:space="preserve">2026-07-01</t>
   </si>
   <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4451682760</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-unilink-ltd-4446581282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator for Computing Qual (testing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-for-computing-qual-testing-at-applied-materials-israel-4449806027</t>
+  </si>
+  <si>
     <t xml:space="preserve">IT Operations Engineer I</t>
   </si>
   <si>
@@ -364,66 +421,6 @@
     <t xml:space="preserve">2026-08-04</t>
   </si>
   <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4451682760</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-unilink-ltd-4446581282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator for Computing Qual (testing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-for-computing-qual-testing-at-applied-materials-israel-4449806027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4377864560</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
     <t xml:space="preserve">AGILINA</t>
   </si>
   <si>
@@ -451,6 +448,36 @@
     <t xml:space="preserve">2026-07-24</t>
   </si>
   <si>
+    <t xml:space="preserve">Moovit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ness Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-moovit-4453119234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
     <t xml:space="preserve">ZyG</t>
   </si>
   <si>
@@ -493,6 +520,24 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-2107-at-tsg-4451506512</t>
   </si>
   <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
     <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
   </si>
   <si>
@@ -505,12 +550,6 @@
     <t xml:space="preserve">2026-07-21</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
   </si>
   <si>
@@ -520,24 +559,6 @@
     <t xml:space="preserve">2026-05-15</t>
   </si>
   <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
     <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
   </si>
   <si>
@@ -580,6 +601,18 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/helpdesk-specialist-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-at-tat-technologies-ltd-4441048130</t>
   </si>
   <si>
+    <t xml:space="preserve">Information Technology Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qb Systems ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-support-engineer-at-qb-systems-ltd-4451539027</t>
+  </si>
+  <si>
     <t xml:space="preserve">IT Service Desk Specialist</t>
   </si>
   <si>
@@ -712,7 +745,7 @@
     <t xml:space="preserve">Azure, Networking, Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-reline-it-solutions-4447384198</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-reline-it-solutions-4450160896</t>
   </si>
   <si>
     <t xml:space="preserve">IT Support Engineer</t>
@@ -754,9 +787,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-extreme-4443366080</t>
   </si>
   <si>
-    <t xml:space="preserve">Information Technology Support Engineer</t>
-  </si>
-  <si>
     <t xml:space="preserve">SISL Global</t>
   </si>
   <si>
@@ -769,27 +799,36 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-support-engineer-at-sisl-global-4440963700</t>
   </si>
   <si>
+    <t xml:space="preserve">Technical Field Operations Technician (IT Support)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Milestone Technologies, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-field-operations-technician-it-support-at-milestone-technologies-inc-4434855297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tata Consultancy Services</t>
   </si>
   <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4446743008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
     <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
   </si>
   <si>
@@ -826,6 +865,21 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-specialist-37157-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4451513171</t>
   </si>
   <si>
+    <t xml:space="preserve">IT Support Engineer (Tier 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HCLTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-tier-2-at-hcltech-4445746731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-29</t>
+  </si>
+  <si>
     <t xml:space="preserve">Employer Branding Student (Temporary )</t>
   </si>
   <si>
@@ -868,46 +922,52 @@
     <t xml:space="preserve">2026-08-09</t>
   </si>
   <si>
-    <t xml:space="preserve">Log-On Software</t>
+    <t xml:space="preserve">IT Support Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-flex-4436841213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phibro Middle East &amp; Europe</t>
   </si>
   <si>
     <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-log-on-software-4449514114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-flex-4436841213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phibro Middle East &amp; Europe</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-specialist-at-phibro-middle-east-europe-4439142494</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M.D. Mechanical Devices Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-m-d-mechanical-devices-ltd-4444118425</t>
+    <t xml:space="preserve">Technical Support Specialist for ROETO - Position No. 1717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBI Investment House</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-for-roeto-position-no-1717-at-ibi-investment-house-4451193725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk &amp; Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipuli Tech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-specialist-at-tipuli-tech-4447121790</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-02</t>
   </si>
   <si>
     <t xml:space="preserve">Working Student, Legal (German)</t>
@@ -922,9 +982,6 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-29</t>
-  </si>
-  <si>
     <t xml:space="preserve">Skill</t>
   </si>
   <si>
@@ -973,6 +1030,12 @@
     <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
   </si>
   <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
+  </si>
+  <si>
     <t xml:space="preserve">CI/CD</t>
   </si>
   <si>
@@ -980,12 +1043,6 @@
   </si>
   <si>
     <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
     <t xml:space="preserve">Azure</t>
@@ -1161,7 +1218,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7">
@@ -1169,7 +1226,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -1185,7 +1242,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>627</v>
+        <v>594</v>
       </c>
     </row>
     <row r="10">
@@ -1267,7 +1324,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22">
@@ -1309,7 +1366,7 @@
         <v>30</v>
       </c>
       <c r="B27" s="3">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28">
@@ -1670,13 +1727,13 @@
         <v>92</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F11" s="3">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>93</v>
@@ -1688,7 +1745,7 @@
         <v>94</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12">
@@ -1696,31 +1753,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F12" s="3">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13">
@@ -1728,31 +1785,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F13" s="3">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>101</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>102</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
@@ -1760,31 +1817,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="3">
+        <v>52</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="H14" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" s="3">
-        <v>51</v>
-      </c>
-      <c r="G14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="15">
@@ -1792,31 +1849,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="E15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="3">
+        <v>51</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="H15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F15" s="3">
-        <v>48</v>
-      </c>
-      <c r="G15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -1824,13 +1881,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>116</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>118</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>26</v>
@@ -1839,16 +1896,16 @@
         <v>48</v>
       </c>
       <c r="G16" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="J16" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="17">
@@ -1856,10 +1913,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>60</v>
@@ -1871,16 +1928,16 @@
         <v>48</v>
       </c>
       <c r="G17" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="J17" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="18">
@@ -1888,13 +1945,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>128</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>26</v>
@@ -1903,13 +1960,13 @@
         <v>48</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>63</v>
@@ -1920,31 +1977,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="E19" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F19" s="3">
+        <v>48</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" s="3">
-        <v>47</v>
-      </c>
-      <c r="G19" s="3" t="s">
+      <c r="H19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="H19" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>134</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="20">
@@ -1952,13 +2009,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>136</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>137</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>26</v>
@@ -1967,16 +2024,16 @@
         <v>40</v>
       </c>
       <c r="G20" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="21">
@@ -1984,10 +2041,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>60</v>
@@ -1999,16 +2056,16 @@
         <v>40</v>
       </c>
       <c r="G21" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>143</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="22">
@@ -2016,19 +2073,19 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F22" s="3">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>146</v>
@@ -2054,13 +2111,13 @@
         <v>150</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>106</v>
+        <v>66</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F23" s="3">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>151</v>
@@ -2080,31 +2137,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" s="3">
+        <v>34</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="H24" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F24" s="3">
-        <v>28</v>
-      </c>
-      <c r="G24" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>157</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="25">
@@ -2112,19 +2169,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="D25" s="3" t="s">
-        <v>66</v>
+        <v>110</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>160</v>
@@ -2150,25 +2207,25 @@
         <v>164</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F26" s="3">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>167</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -2286,7 +2343,7 @@
         <v>47</v>
       </c>
       <c r="K2" s="3">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3">
@@ -2321,7 +2378,7 @@
         <v>52</v>
       </c>
       <c r="K3" s="3">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4">
@@ -2356,7 +2413,7 @@
         <v>57</v>
       </c>
       <c r="K4" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -2391,7 +2448,7 @@
         <v>63</v>
       </c>
       <c r="K5" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -2426,7 +2483,7 @@
         <v>69</v>
       </c>
       <c r="K6" s="3">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7">
@@ -2461,7 +2518,7 @@
         <v>75</v>
       </c>
       <c r="K7" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -2496,7 +2553,7 @@
         <v>57</v>
       </c>
       <c r="K8" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -2531,7 +2588,7 @@
         <v>63</v>
       </c>
       <c r="K9" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -2566,7 +2623,7 @@
         <v>90</v>
       </c>
       <c r="K10" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
@@ -2577,13 +2634,13 @@
         <v>92</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E11" s="3">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>93</v>
@@ -2598,62 +2655,62 @@
         <v>94</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="K11" s="3">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E12" s="3">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>173</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="K12" s="3">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E13" s="3">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>101</v>
@@ -2662,97 +2719,97 @@
         <v>173</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>102</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="K13" s="3">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" s="3">
+        <v>52</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="G14" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" s="3">
-        <v>51</v>
-      </c>
-      <c r="F14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>109</v>
-      </c>
       <c r="K14" s="3">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="D15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="3">
+        <v>51</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="G15" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" s="3">
-        <v>48</v>
-      </c>
-      <c r="F15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>115</v>
-      </c>
       <c r="K15" s="3">
-        <v>8</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>116</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>118</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>26</v>
@@ -2761,30 +2818,30 @@
         <v>48</v>
       </c>
       <c r="F16" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="J16" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>121</v>
-      </c>
       <c r="K16" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>60</v>
@@ -2796,33 +2853,33 @@
         <v>48</v>
       </c>
       <c r="F17" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="J17" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>125</v>
-      </c>
       <c r="K17" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>128</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>26</v>
@@ -2831,7 +2888,7 @@
         <v>48</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>173</v>
@@ -2840,59 +2897,59 @@
         <v>30</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>63</v>
       </c>
       <c r="K18" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="D19" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" s="3">
+        <v>48</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E19" s="3">
-        <v>47</v>
-      </c>
-      <c r="F19" s="3" t="s">
+      <c r="G19" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="J19" s="3" t="s">
-        <v>135</v>
-      </c>
       <c r="K19" s="3">
-        <v>73</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>136</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>137</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>26</v>
@@ -2901,30 +2958,30 @@
         <v>40</v>
       </c>
       <c r="F20" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="K20" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>60</v>
@@ -2936,39 +2993,39 @@
         <v>40</v>
       </c>
       <c r="F21" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>144</v>
-      </c>
       <c r="K21" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E22" s="3">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>146</v>
@@ -2986,7 +3043,7 @@
         <v>148</v>
       </c>
       <c r="K22" s="3">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2997,13 +3054,13 @@
         <v>150</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>106</v>
+        <v>66</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E23" s="3">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>151</v>
@@ -3021,59 +3078,59 @@
         <v>153</v>
       </c>
       <c r="K23" s="3">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="C24" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E24" s="3">
+        <v>34</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="G24" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E24" s="3">
-        <v>28</v>
-      </c>
-      <c r="F24" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>63</v>
-      </c>
       <c r="K24" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="C25" s="3" t="s">
-        <v>66</v>
+        <v>110</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>160</v>
@@ -3091,7 +3148,7 @@
         <v>162</v>
       </c>
       <c r="K25" s="3">
-        <v>22</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26">
@@ -3102,16 +3159,16 @@
         <v>164</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E26" s="3">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>173</v>
@@ -3120,13 +3177,13 @@
         <v>30</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>167</v>
+        <v>63</v>
       </c>
       <c r="K26" s="3">
-        <v>89</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -3134,80 +3191,80 @@
         <v>174</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>175</v>
+        <v>59</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>176</v>
+        <v>66</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E27" s="3">
+        <v>27</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="K27" s="3">
         <v>23</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="K27" s="3">
-        <v>26</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E28" s="3">
+        <v>24</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="J28" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E28" s="3">
-        <v>23</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="K28" s="3">
-        <v>28</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>183</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>185</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>25</v>
@@ -3216,112 +3273,112 @@
         <v>23</v>
       </c>
       <c r="F29" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="J29" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>144</v>
-      </c>
       <c r="K29" s="3">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E30" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>173</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="K30" s="3">
-        <v>89</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E31" s="3">
+        <v>23</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="K31" s="3">
         <v>20</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="K31" s="3">
-        <v>24</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>201</v>
+        <v>60</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E32" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>173</v>
@@ -3330,24 +3387,24 @@
         <v>30</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>115</v>
+        <v>63</v>
       </c>
       <c r="K32" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>25</v>
@@ -3356,42 +3413,42 @@
         <v>20</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>173</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>209</v>
+        <v>180</v>
       </c>
       <c r="K33" s="3">
-        <v>27</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E34" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>173</v>
@@ -3400,33 +3457,33 @@
         <v>30</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="K34" s="3">
-        <v>6</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E35" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>173</v>
@@ -3435,33 +3492,33 @@
         <v>30</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>221</v>
+        <v>134</v>
       </c>
       <c r="K35" s="3">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>164</v>
+        <v>216</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>82</v>
+        <v>217</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E36" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>173</v>
@@ -3470,24 +3527,24 @@
         <v>30</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="K36" s="3">
-        <v>6</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>25</v>
@@ -3496,7 +3553,7 @@
         <v>17</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>173</v>
@@ -3505,24 +3562,24 @@
         <v>30</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="K37" s="3">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B38" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>229</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>230</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>25</v>
@@ -3531,22 +3588,22 @@
         <v>17</v>
       </c>
       <c r="F38" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I38" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="G38" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I38" s="3" t="s">
+      <c r="J38" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="J38" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="K38" s="3">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="39">
@@ -3554,10 +3611,10 @@
         <v>233</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>234</v>
+        <v>92</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>235</v>
+        <v>82</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>25</v>
@@ -3566,7 +3623,7 @@
         <v>17</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>173</v>
@@ -3575,68 +3632,68 @@
         <v>30</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>125</v>
+        <v>226</v>
       </c>
       <c r="K39" s="3">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="C40" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E40" s="3">
+        <v>17</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I40" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="D40" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E40" s="3">
-        <v>13</v>
-      </c>
-      <c r="F40" s="3" t="s">
+      <c r="J40" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="G40" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>241</v>
-      </c>
       <c r="K40" s="3">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>206</v>
+        <v>241</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E41" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>173</v>
@@ -3645,138 +3702,138 @@
         <v>30</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>98</v>
+        <v>148</v>
       </c>
       <c r="K41" s="3">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C42" s="3" t="s">
         <v>246</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>248</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E42" s="3">
+        <v>17</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="K42" s="3">
         <v>13</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="K42" s="3">
-        <v>27</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>163</v>
+        <v>248</v>
       </c>
       <c r="B43" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E43" s="3">
+        <v>13</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I43" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="C43" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E43" s="3">
-        <v>12</v>
-      </c>
-      <c r="F43" s="3" t="s">
+      <c r="J43" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>121</v>
-      </c>
       <c r="K43" s="3">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>255</v>
-      </c>
       <c r="C44" s="3" t="s">
-        <v>256</v>
+        <v>217</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E44" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>173</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="K44" s="3">
-        <v>80</v>
+        <v>22</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>242</v>
+        <v>195</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>66</v>
+        <v>258</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E45" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>173</v>
@@ -3785,13 +3842,13 @@
         <v>30</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>260</v>
+        <v>220</v>
       </c>
       <c r="K45" s="3">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="46">
@@ -3802,16 +3859,16 @@
         <v>262</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E46" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>173</v>
@@ -3820,24 +3877,24 @@
         <v>30</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>63</v>
+        <v>226</v>
       </c>
       <c r="K46" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>104</v>
+        <v>265</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>66</v>
+        <v>267</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>25</v>
@@ -3846,42 +3903,42 @@
         <v>10</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>173</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>52</v>
       </c>
       <c r="K47" s="3">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E48" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>173</v>
@@ -3890,30 +3947,30 @@
         <v>30</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>63</v>
+        <v>273</v>
       </c>
       <c r="K48" s="3">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>86</v>
+        <v>275</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E49" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>271</v>
@@ -3922,36 +3979,36 @@
         <v>173</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>273</v>
+        <v>63</v>
       </c>
       <c r="K49" s="3">
-        <v>41</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>274</v>
+        <v>108</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>276</v>
+        <v>66</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E50" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>173</v>
@@ -3960,30 +4017,30 @@
         <v>30</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>115</v>
+        <v>52</v>
       </c>
       <c r="K50" s="3">
-        <v>8</v>
+        <v>81</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>112</v>
+        <v>82</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E51" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>281</v>
@@ -3998,27 +4055,27 @@
         <v>282</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>283</v>
+        <v>63</v>
       </c>
       <c r="K51" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>242</v>
+        <v>283</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>284</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>137</v>
+        <v>60</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E52" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>285</v>
@@ -4036,7 +4093,7 @@
         <v>287</v>
       </c>
       <c r="K52" s="3">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="53">
@@ -4044,34 +4101,34 @@
         <v>288</v>
       </c>
       <c r="B53" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E53" s="3">
+        <v>4</v>
+      </c>
+      <c r="F53" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="C53" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E53" s="3">
-        <v>3</v>
-      </c>
-      <c r="F53" s="3" t="s">
+      <c r="G53" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I53" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="G53" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I53" s="3" t="s">
+      <c r="J53" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="J53" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="K53" s="3">
-        <v>28</v>
+        <v>42</v>
       </c>
     </row>
     <row r="54">
@@ -4082,7 +4139,7 @@
         <v>293</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>82</v>
+        <v>294</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>25</v>
@@ -4091,7 +4148,7 @@
         <v>3</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>173</v>
@@ -4100,24 +4157,24 @@
         <v>30</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>295</v>
+        <v>134</v>
       </c>
       <c r="K54" s="3">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>131</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>218</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>25</v>
@@ -4126,7 +4183,7 @@
         <v>3</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>173</v>
@@ -4135,50 +4192,190 @@
         <v>30</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>260</v>
+        <v>301</v>
       </c>
       <c r="K55" s="3">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>300</v>
+        <v>183</v>
       </c>
       <c r="D56" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E56" s="3">
+        <v>3</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="K56" s="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E57" s="3">
+        <v>3</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="K57" s="3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E58" s="3">
+        <v>3</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="K58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E59" s="3">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="K59" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="D60" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E56" s="3">
+      <c r="E60" s="3">
         <v>0</v>
       </c>
-      <c r="F56" s="3"/>
-      <c r="G56" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H56" s="3" t="s">
+      <c r="F60" s="3"/>
+      <c r="G60" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H60" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="I56" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="J56" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="K56" s="3">
-        <v>14</v>
+      <c r="I60" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="K60" s="3">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K56"/>
+  <autoFilter ref="A1:K60"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -4235,6 +4432,10 @@
     <hyperlink ref="I54" r:id="rId53"/>
     <hyperlink ref="I55" r:id="rId54"/>
     <hyperlink ref="I56" r:id="rId55"/>
+    <hyperlink ref="I57" r:id="rId56"/>
+    <hyperlink ref="I58" r:id="rId57"/>
+    <hyperlink ref="I59" r:id="rId58"/>
+    <hyperlink ref="I60" r:id="rId59"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4242,9 +4443,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="37" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -4276,55 +4477,79 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D2" s="3">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>163</v>
+        <v>233</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>121</v>
+        <v>148</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="3">
+        <v>3</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G4"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
+    <hyperlink ref="F4" r:id="rId3"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4339,178 +4564,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>303</v>
+        <v>322</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>304</v>
+        <v>323</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>305</v>
+        <v>324</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="B2" s="3">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>306</v>
+        <v>325</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="B3" s="3">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>307</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>308</v>
+        <v>327</v>
       </c>
       <c r="B4" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>309</v>
+        <v>328</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>271</v>
+        <v>289</v>
       </c>
       <c r="B5" s="3">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>310</v>
+        <v>329</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>311</v>
+        <v>330</v>
       </c>
       <c r="B6" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>313</v>
+        <v>332</v>
       </c>
       <c r="B7" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>314</v>
+        <v>333</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="B8" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>316</v>
+        <v>335</v>
       </c>
       <c r="B9" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>317</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>285</v>
+        <v>308</v>
       </c>
       <c r="B10" s="3">
         <v>17</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>318</v>
+        <v>337</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>319</v>
+        <v>338</v>
       </c>
       <c r="B11" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>320</v>
+        <v>339</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>277</v>
+        <v>340</v>
       </c>
       <c r="B12" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>321</v>
+        <v>341</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>322</v>
+        <v>295</v>
       </c>
       <c r="B13" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>323</v>
+        <v>342</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>324</v>
+        <v>343</v>
       </c>
       <c r="B14" s="3">
         <v>10</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>325</v>
+        <v>344</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>326</v>
+        <v>345</v>
       </c>
       <c r="B15" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>327</v>
+        <v>346</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>328</v>
+        <v>347</v>
       </c>
       <c r="B16" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>329</v>
+        <v>348</v>
       </c>
     </row>
   </sheetData>
@@ -4530,10 +4755,10 @@
         <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>330</v>
+        <v>349</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>331</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2">
@@ -4541,10 +4766,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>332</v>
+        <v>351</v>
       </c>
     </row>
     <row r="3">
@@ -4555,7 +4780,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>333</v>
+        <v>352</v>
       </c>
     </row>
     <row r="4">
@@ -4566,7 +4791,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>334</v>
+        <v>353</v>
       </c>
     </row>
     <row r="5">
@@ -4577,7 +4802,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>335</v>
+        <v>354</v>
       </c>
     </row>
   </sheetData>
@@ -4598,13 +4823,13 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>336</v>
+        <v>355</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>337</v>
+        <v>356</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>338</v>
+        <v>357</v>
       </c>
     </row>
     <row r="2">
@@ -4615,7 +4840,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>339</v>
+        <v>358</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -4624,22 +4849,22 @@
         <v>30</v>
       </c>
       <c r="B3" s="3">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>339</v>
+        <v>358</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>340</v>
+        <v>359</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>339</v>
+        <v>358</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W33.xlsx
+++ b/reports/devops-juniors-israel-2026-W33.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="412">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-13T07:48:19</t>
+    <t xml:space="preserve">2026-08-14T07:46:18</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -142,6 +142,24 @@
     <t xml:space="preserve">First Seen</t>
   </si>
   <si>
+    <t xml:space="preserve">DevOps Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axonius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, CI/CD, Git, Terraform/IaC, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7818899003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-30</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior AI SRE Developer</t>
   </si>
   <si>
@@ -160,895 +178,1033 @@
     <t xml:space="preserve">2026-06-02</t>
   </si>
   <si>
+    <t xml:space="preserve">software development student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Terraform/IaC, Networking, Virtualization, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-development-student-at-radware-4452112960</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
     <t xml:space="preserve">Linux System Administrator</t>
   </si>
   <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4448158765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4452408106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Release Engineering Intern (Part-Time, 80%, One-year temporary position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8069193?gh_jid=8069193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waterfall Security Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-position-at-waterfall-security-solutions-4444878648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4454032601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test Environment Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-environment-support-engineer-at-abra-4442615924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4442889333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MER Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Networking, Monitoring, Virtualization, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-mer-group-4436525380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PlainID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-plainid-4451417266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tenzai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-tenzai-4448410816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anecdotes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">etoro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator for Computing Qual (testing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-for-computing-qual-testing-at-applied-materials-israel-4449806027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist – MENTEE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-%E2%80%93-mentee-at-mobileye-4445729205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Candex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-candex-4454009475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations &amp; Security Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PointFive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-security-specialist-at-pointfive-4426311043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moovit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ness Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-moovit-4453119234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-anecdotes-4437847270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support - Tier 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Monitoring, Databases, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-tier-2-at-duve-4451510957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-comblack-4454021597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reline IT Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-reline-it-solutions-4450457986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP, Cloud (any), Git, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-administrator-at-skai-4451634323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spinomenal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - 2107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-2107-at-tsg-4451506512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT &amp; System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeen.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-administrator-at-jeen-ai-4452428733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator- Microsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-microsoft-at-abra-4451111887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (36859)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-36859-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4453698899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer 2, Technical Operations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4444274357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician - Modiin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-modiin-at-nebius-4437655752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician - Beit Shemesh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-beit-shemesh-at-nebius-4437673265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qb Systems ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-support-engineer-at-qb-systems-ltd-4451539027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helpdesk Specialist טכנאי/ת תמיכה טכנית</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAT Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiryat Gat, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/helpdesk-specialist-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-at-tat-technologies-ltd-4441048130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Septier Communication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-septier-communication-4450134431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Development Student, AWS Annapurna Labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-development-student-aws-annapurna-labs-at-amazon-web-services-aws-4443046179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23343 - IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualitest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/23343-it-support-specialist-at-qualitest-4447935579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">איש/אשת תמיכה טכנית ו -Helpdesk 2+בפתח תקווה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arad Tech - Technology, Engineering &amp; AI Recruitment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-%D7%95-helpdesk-2%2B%D7%91%D7%A4%D7%AA%D7%97-%D7%AA%D7%A7%D7%95%D7%95%D7%94-at-arad-tech-technology-engineering-ai-recruitment-4440622529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer - Entry Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-entry-level-at-check-point-software-4441459886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technical Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiverr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technical-support-at-fiverr-4449741839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lab Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lab-support-engineer-at-harmonic-4448547160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-technician-at-energean-4443137036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airobotics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-airobotics-4439190133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-reline-it-solutions-4450160896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-confidential-4444582152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budapest, Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SISL Global</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-support-engineer-at-sisl-global-4440963700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Field Operations Technician (IT Support)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Milestone Technologies, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-field-operations-technician-it-support-at-milestone-technologies-inc-4434855297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gravity Forms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git, Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-gravity-forms-4450978605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior NOC Engineer | Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-On Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-noc-engineer-student-position-at-log-on-software-4450132712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WaveBL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0Aisrael-at-wavebl-4443917908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
   </si>
   <si>
     <t xml:space="preserve">2026-05-24</t>
   </si>
   <si>
-    <t xml:space="preserve">Calanit by one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4448158765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4452408106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Release Engineering Intern (Part-Time, 80%, One-year temporary position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8069193?gh_jid=8069193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waterfall Security Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-position-at-waterfall-security-solutions-4444878648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4451564107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test Environment Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-environment-support-engineer-at-abra-4442615924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4442889333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator &amp; IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inManage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">etoro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4451682760</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-unilink-ltd-4446581282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator for Computing Qual (testing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-for-computing-qual-testing-at-applied-materials-israel-4449806027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations Engineer I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innovid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-engineer-i-at-innovid-4443857656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGILINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Networking, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-agilina-4448561239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QuantHealth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-quanthealth-4444080917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moovit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ness Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-moovit-4453119234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+    <t xml:space="preserve">Field IT Technician (36179)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-technician-36179-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4453695689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Application Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global-e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/application-support-engineer-at-global-e-4443383037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Galooli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/customer-technical-support-specialist-at-galooli-4432181954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">תמיכה טכנית</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StoreNext</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-at-storenext-4438985234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meitar | Law Offices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4450505697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phibro Middle East &amp; Europe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-specialist-at-phibro-middle-east-europe-4439142494</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-13</t>
   </si>
   <si>
-    <t xml:space="preserve">ZyG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Git, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-zyg-4441776623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spinomenal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - 2107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-2107-at-tsg-4451506512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4442592331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Modiin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-modiin-at-nebius-4437655752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helpdesk Specialist טכנאי/ת תמיכה טכנית</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAT Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiryat Gat, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/helpdesk-specialist-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-at-tat-technologies-ltd-4441048130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">qb Systems ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-support-engineer-at-qb-systems-ltd-4451539027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Field IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magal Security Systems (India) Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magal, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Databases, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-technician-at-magal-security-systems-india-ltd-4442431214</t>
+    <t xml:space="preserve">תמיכה טכנית - מערכת Meteor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-%D7%9E%D7%A2%D7%A8%D7%9B%D7%AA-meteor-at-storenext-4440240961</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-19</t>
   </si>
   <si>
-    <t xml:space="preserve">23343 - IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualitest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/23343-it-support-specialist-at-qualitest-4447935579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">איש/אשת תמיכה טכנית ו -Helpdesk 2+בפתח תקווה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arad Tech - Technology, Engineering &amp; AI Recruitment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-%D7%95-helpdesk-2%2B%D7%91%D7%A4%D7%AA%D7%97-%D7%AA%D7%A7%D7%95%D7%95%D7%94-at-arad-tech-technology-engineering-ai-recruitment-4440622529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lab Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lab-support-engineer-at-harmonic-4448547160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Energean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-technician-at-energean-4443137036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4449365989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airobotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-airobotics-4439190133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reline IT Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-reline-it-solutions-4450160896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-confidential-4444582152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budapest, Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-extreme-4443366080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SISL Global</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-support-engineer-at-sisl-global-4440963700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Field Operations Technician (IT Support)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Milestone Technologies, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-field-operations-technician-it-support-at-milestone-technologies-inc-4434855297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4446732076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Field IT Technician (36179)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-technician-36179-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4451516191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RealPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Support Specialist (37157)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-specialist-37157-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4451513171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Engineer (Tier 2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HCLTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-tier-2-at-hcltech-4445746731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">טכנאי/ת Help desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givat Shmuel, Center District, Israel</t>
+    <t xml:space="preserve">Bulwarx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-bulwarx-4451114923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist for ROETO - Position No. 1717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBI Investment House</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-for-roeto-position-no-1717-at-ibi-investment-house-4451193725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-walkme-4374713618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Configo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-configo-4450146088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Working Student, Legal (German)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Via</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berlin, Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
   </si>
   <si>
     <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4448140764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meitar | Law Offices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4450505697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-flex-4436841213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phibro Middle East &amp; Europe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-specialist-at-phibro-middle-east-europe-4439142494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist for ROETO - Position No. 1717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IBI Investment House</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-for-roeto-position-no-1717-at-ibi-investment-house-4451193725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk &amp; Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tipuli Tech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-specialist-at-tipuli-tech-4447121790</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Working Student, Legal (German)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Via</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berlin, Germany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
-  </si>
-  <si>
     <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
     <t xml:space="preserve">Docker</t>
@@ -1218,7 +1374,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>59</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7">
@@ -1226,7 +1382,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>3</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8">
@@ -1234,7 +1390,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9">
@@ -1242,7 +1398,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>594</v>
+        <v>621</v>
       </c>
     </row>
     <row r="10">
@@ -1324,7 +1480,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>36</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22">
@@ -1332,7 +1488,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23">
@@ -1340,7 +1496,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -1366,7 +1522,7 @@
         <v>30</v>
       </c>
       <c r="B27" s="3">
-        <v>51</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28">
@@ -1374,7 +1530,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1386,7 +1542,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="37" customWidth="1"/>
+    <col min="3" max="3" width="32" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -1442,7 +1598,7 @@
         <v>44</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
@@ -1451,7 +1607,7 @@
         <v>45</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>46</v>
@@ -1471,25 +1627,25 @@
         <v>49</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4">
@@ -1497,31 +1653,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5">
@@ -1529,13 +1685,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>26</v>
@@ -1544,16 +1700,16 @@
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6">
@@ -1561,13 +1717,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>26</v>
@@ -1576,16 +1732,16 @@
         <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7">
@@ -1593,31 +1749,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F7" s="3">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8">
@@ -1625,13 +1781,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>27</v>
@@ -1643,13 +1799,13 @@
         <v>79</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>80</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9">
@@ -1657,31 +1813,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F9" s="3">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10">
@@ -1689,31 +1845,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F10" s="3">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>90</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11">
@@ -1727,25 +1883,25 @@
         <v>92</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F11" s="3">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12">
@@ -1753,31 +1909,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F12" s="3">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
@@ -1785,31 +1941,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F13" s="3">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14">
@@ -1817,31 +1973,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>66</v>
+        <v>108</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F14" s="3">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -1849,31 +2005,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>110</v>
+        <v>68</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F15" s="3">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>113</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16">
@@ -1881,19 +2037,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>116</v>
+        <v>68</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F16" s="3">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>117</v>
@@ -1905,7 +2061,7 @@
         <v>118</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>119</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17">
@@ -1913,19 +2069,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>120</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>121</v>
@@ -1948,28 +2104,28 @@
         <v>124</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>125</v>
+        <v>92</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>126</v>
+        <v>93</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F18" s="3">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19">
@@ -1977,31 +2133,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>131</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F19" s="3">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="G19" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J19" s="3" t="s">
         <v>132</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="20">
@@ -2009,31 +2165,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>136</v>
+        <v>56</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F20" s="3">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G20" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="21">
@@ -2041,31 +2197,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="C21" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="3">
+        <v>51</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F21" s="3">
-        <v>40</v>
-      </c>
-      <c r="G21" s="3" t="s">
+      <c r="H21" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>142</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="22">
@@ -2073,7 +2229,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>108</v>
+        <v>143</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>144</v>
@@ -2082,10 +2238,10 @@
         <v>145</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F22" s="3">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>146</v>
@@ -2097,7 +2253,7 @@
         <v>147</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>148</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23">
@@ -2105,31 +2261,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="3">
+        <v>47</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F23" s="3">
-        <v>36</v>
-      </c>
-      <c r="G23" s="3" t="s">
+      <c r="H23" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="24">
@@ -2137,31 +2293,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>108</v>
+        <v>153</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>154</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>66</v>
+        <v>155</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>157</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25">
@@ -2175,13 +2331,13 @@
         <v>159</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>110</v>
+        <v>68</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F25" s="3">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>160</v>
@@ -2193,7 +2349,7 @@
         <v>161</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>162</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26">
@@ -2201,31 +2357,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="E26" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26" s="3">
+        <v>37</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="H26" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="E26" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F26" s="3">
-        <v>28</v>
-      </c>
-      <c r="G26" s="3" t="s">
+      <c r="J26" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -2278,7 +2434,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>34</v>
@@ -2293,22 +2449,22 @@
         <v>37</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>170</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>39</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>41</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2">
@@ -2322,7 +2478,7 @@
         <v>44</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E2" s="3">
         <v>100</v>
@@ -2331,10 +2487,10 @@
         <v>45</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>46</v>
@@ -2343,7 +2499,7 @@
         <v>47</v>
       </c>
       <c r="K2" s="3">
-        <v>72</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -2354,77 +2510,77 @@
         <v>49</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E3" s="3">
         <v>100</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K3" s="3">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E4" s="3">
         <v>100</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K4" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>26</v>
@@ -2433,33 +2589,33 @@
         <v>100</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K5" s="3">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>26</v>
@@ -2468,68 +2624,68 @@
         <v>100</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K6" s="3">
-        <v>62</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E7" s="3">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K7" s="3">
-        <v>16</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>27</v>
@@ -2541,89 +2697,89 @@
         <v>79</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>80</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="K8" s="3">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E9" s="3">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K9" s="3">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E10" s="3">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="K10" s="3">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -2634,194 +2790,194 @@
         <v>92</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E11" s="3">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K11" s="3">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E12" s="3">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="K12" s="3">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E13" s="3">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K13" s="3">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>66</v>
+        <v>108</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E14" s="3">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="K14" s="3">
-        <v>44</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>110</v>
+        <v>68</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E15" s="3">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>113</v>
+        <v>59</v>
       </c>
       <c r="K15" s="3">
-        <v>43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>116</v>
+        <v>68</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E16" s="3">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>117</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>30</v>
@@ -2830,33 +2986,33 @@
         <v>118</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>119</v>
+        <v>59</v>
       </c>
       <c r="K16" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>120</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>121</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>30</v>
@@ -2868,7 +3024,7 @@
         <v>123</v>
       </c>
       <c r="K17" s="3">
-        <v>13</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18">
@@ -2876,144 +3032,144 @@
         <v>124</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>125</v>
+        <v>92</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>126</v>
+        <v>93</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E18" s="3">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="K18" s="3">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>131</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E19" s="3">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="F19" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J19" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>134</v>
-      </c>
       <c r="K19" s="3">
-        <v>9</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>136</v>
+        <v>56</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E20" s="3">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="F20" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>139</v>
-      </c>
       <c r="K20" s="3">
-        <v>8</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="3">
+        <v>51</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E21" s="3">
-        <v>40</v>
-      </c>
-      <c r="F21" s="3" t="s">
+      <c r="G21" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>143</v>
-      </c>
       <c r="K21" s="3">
-        <v>20</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>108</v>
+        <v>143</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>144</v>
@@ -3022,16 +3178,16 @@
         <v>145</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E22" s="3">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>146</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>30</v>
@@ -3040,80 +3196,80 @@
         <v>147</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>148</v>
+        <v>71</v>
       </c>
       <c r="K22" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" s="3">
+        <v>47</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E23" s="3">
-        <v>36</v>
-      </c>
-      <c r="F23" s="3" t="s">
+      <c r="G23" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>153</v>
-      </c>
       <c r="K23" s="3">
-        <v>31</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>108</v>
+        <v>153</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>154</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>66</v>
+        <v>155</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>157</v>
+        <v>59</v>
       </c>
       <c r="K24" s="3">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -3124,19 +3280,19 @@
         <v>159</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>110</v>
+        <v>68</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E25" s="3">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>160</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>30</v>
@@ -3145,115 +3301,115 @@
         <v>161</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>162</v>
+        <v>59</v>
       </c>
       <c r="K25" s="3">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="D26" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E26" s="3">
+        <v>37</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="G26" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E26" s="3">
-        <v>28</v>
-      </c>
-      <c r="F26" s="3" t="s">
+      <c r="J26" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>63</v>
-      </c>
       <c r="K26" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E27" s="3">
+        <v>37</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E27" s="3">
-        <v>27</v>
-      </c>
-      <c r="F27" s="3" t="s">
+      <c r="G27" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I27" s="3" t="s">
+      <c r="J27" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>177</v>
-      </c>
       <c r="K27" s="3">
-        <v>23</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>149</v>
+        <v>177</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>92</v>
+        <v>178</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E28" s="3">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>180</v>
+        <v>59</v>
       </c>
       <c r="K28" s="3">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -3261,976 +3417,976 @@
         <v>181</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E29" s="3">
+        <v>36</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="G29" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E29" s="3">
-        <v>23</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>185</v>
-      </c>
       <c r="J29" s="3" t="s">
-        <v>186</v>
+        <v>59</v>
       </c>
       <c r="K29" s="3">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E30" s="3">
+        <v>36</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I30" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E30" s="3">
-        <v>23</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>188</v>
-      </c>
       <c r="J30" s="3" t="s">
-        <v>189</v>
+        <v>59</v>
       </c>
       <c r="K30" s="3">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E31" s="3">
+        <v>32</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="G31" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I31" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E31" s="3">
-        <v>23</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>194</v>
-      </c>
       <c r="J31" s="3" t="s">
-        <v>143</v>
+        <v>59</v>
       </c>
       <c r="K31" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E32" s="3">
+        <v>30</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I32" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="J32" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E32" s="3">
-        <v>23</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>63</v>
-      </c>
       <c r="K32" s="3">
-        <v>2</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="D33" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E33" s="3">
+        <v>28</v>
+      </c>
+      <c r="F33" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="G33" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I33" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E33" s="3">
-        <v>20</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>203</v>
-      </c>
       <c r="J33" s="3" t="s">
-        <v>180</v>
+        <v>71</v>
       </c>
       <c r="K33" s="3">
-        <v>90</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E34" s="3">
+        <v>28</v>
+      </c>
+      <c r="F34" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="G34" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E34" s="3">
-        <v>20</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>208</v>
-      </c>
       <c r="J34" s="3" t="s">
-        <v>209</v>
+        <v>59</v>
       </c>
       <c r="K34" s="3">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>211</v>
+        <v>98</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E35" s="3">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>134</v>
+        <v>59</v>
       </c>
       <c r="K35" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>215</v>
+        <v>173</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E36" s="3">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>220</v>
+        <v>59</v>
       </c>
       <c r="K36" s="3">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>223</v>
+        <v>88</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E37" s="3">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>226</v>
+        <v>59</v>
       </c>
       <c r="K37" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E38" s="3">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>232</v>
+        <v>59</v>
       </c>
       <c r="K38" s="3">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>92</v>
+        <v>224</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>82</v>
+        <v>225</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E39" s="3">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K39" s="3">
-        <v>7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E40" s="3">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>239</v>
+        <v>59</v>
       </c>
       <c r="K40" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E41" s="3">
+        <v>23</v>
+      </c>
+      <c r="F41" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E41" s="3">
-        <v>17</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>242</v>
-      </c>
       <c r="G41" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>148</v>
+        <v>71</v>
       </c>
       <c r="K41" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E42" s="3">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>123</v>
+        <v>240</v>
       </c>
       <c r="K42" s="3">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>248</v>
+        <v>173</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>71</v>
+        <v>241</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>249</v>
+        <v>220</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E43" s="3">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>252</v>
+        <v>59</v>
       </c>
       <c r="K43" s="3">
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E44" s="3">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="K44" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>195</v>
+        <v>248</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E45" s="3">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>220</v>
+        <v>59</v>
       </c>
       <c r="K45" s="3">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>66</v>
+        <v>255</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E46" s="3">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>226</v>
+        <v>258</v>
       </c>
       <c r="K46" s="3">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>267</v>
+        <v>220</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E47" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>52</v>
+        <v>263</v>
       </c>
       <c r="K47" s="3">
-        <v>81</v>
+        <v>29</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E48" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>273</v>
+        <v>59</v>
       </c>
       <c r="K48" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E49" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>271</v>
+        <v>251</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="K49" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>108</v>
+        <v>271</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>66</v>
+        <v>273</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E50" s="3">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>52</v>
+        <v>276</v>
       </c>
       <c r="K50" s="3">
-        <v>81</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E51" s="3">
+        <v>17</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I51" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="B51" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E51" s="3">
-        <v>6</v>
-      </c>
-      <c r="F51" s="3" t="s">
+      <c r="J51" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="G51" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="J51" s="3" t="s">
-        <v>63</v>
-      </c>
       <c r="K51" s="3">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="C52" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E52" s="3">
+        <v>17</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I52" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="C52" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E52" s="3">
-        <v>6</v>
-      </c>
-      <c r="F52" s="3" t="s">
+      <c r="J52" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>287</v>
-      </c>
       <c r="K52" s="3">
-        <v>15</v>
+        <v>31</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E53" s="3">
+        <v>17</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I53" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="B53" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E53" s="3">
-        <v>4</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I53" s="3" t="s">
-        <v>290</v>
-      </c>
       <c r="J53" s="3" t="s">
-        <v>291</v>
+        <v>166</v>
       </c>
       <c r="K53" s="3">
-        <v>42</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E54" s="3">
+        <v>17</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="J54" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="B54" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E54" s="3">
-        <v>3</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>134</v>
-      </c>
       <c r="K54" s="3">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E55" s="3">
+        <v>13</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="J55" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="B55" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E55" s="3">
-        <v>3</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I55" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="J55" s="3" t="s">
-        <v>301</v>
-      </c>
       <c r="K55" s="3">
-        <v>4</v>
+        <v>37</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>302</v>
+        <v>231</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>183</v>
+        <v>129</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E56" s="3">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>189</v>
+        <v>263</v>
       </c>
       <c r="K56" s="3">
         <v>29</v>
@@ -4238,144 +4394,669 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E57" s="3">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>153</v>
+        <v>276</v>
       </c>
       <c r="K57" s="3">
-        <v>31</v>
+        <v>8</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>310</v>
+        <v>173</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>60</v>
+        <v>306</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E58" s="3">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>148</v>
+        <v>309</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E59" s="3">
+        <v>12</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I59" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="B59" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E59" s="3">
-        <v>3</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>316</v>
-      </c>
       <c r="J59" s="3" t="s">
-        <v>317</v>
+        <v>59</v>
       </c>
       <c r="K59" s="3">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E60" s="3">
+        <v>12</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="B61" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="C61" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="D60" s="3" t="s">
+      <c r="D61" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E61" s="3">
+        <v>10</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="K61" s="3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E62" s="3">
+        <v>10</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E63" s="3">
+        <v>10</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E64" s="3">
+        <v>10</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="K64" s="3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E65" s="3">
+        <v>6</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="K65" s="3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E66" s="3">
+        <v>6</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="K66" s="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D67" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E60" s="3">
+      <c r="E67" s="3">
+        <v>4</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="K67" s="3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E68" s="3">
+        <v>3</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="K68" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E69" s="3">
+        <v>3</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="K69" s="3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E70" s="3">
+        <v>3</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="K70" s="3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E71" s="3">
+        <v>3</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K71" s="3">
         <v>0</v>
       </c>
-      <c r="F60" s="3"/>
-      <c r="G60" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H60" s="3" t="s">
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E72" s="3">
+        <v>3</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="K72" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E73" s="3">
+        <v>3</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="J73" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="K73" s="3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E74" s="3">
+        <v>3</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E75" s="3">
+        <v>0</v>
+      </c>
+      <c r="F75" s="3"/>
+      <c r="G75" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H75" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="K60" s="3">
-        <v>15</v>
+      <c r="I75" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="J75" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="K75" s="3">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K60"/>
+  <autoFilter ref="A1:K75"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -4436,6 +5117,21 @@
     <hyperlink ref="I58" r:id="rId57"/>
     <hyperlink ref="I59" r:id="rId58"/>
     <hyperlink ref="I60" r:id="rId59"/>
+    <hyperlink ref="I61" r:id="rId60"/>
+    <hyperlink ref="I62" r:id="rId61"/>
+    <hyperlink ref="I63" r:id="rId62"/>
+    <hyperlink ref="I64" r:id="rId63"/>
+    <hyperlink ref="I65" r:id="rId64"/>
+    <hyperlink ref="I66" r:id="rId65"/>
+    <hyperlink ref="I67" r:id="rId66"/>
+    <hyperlink ref="I68" r:id="rId67"/>
+    <hyperlink ref="I69" r:id="rId68"/>
+    <hyperlink ref="I70" r:id="rId69"/>
+    <hyperlink ref="I71" r:id="rId70"/>
+    <hyperlink ref="I72" r:id="rId71"/>
+    <hyperlink ref="I73" r:id="rId72"/>
+    <hyperlink ref="I74" r:id="rId73"/>
+    <hyperlink ref="I75" r:id="rId74"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4443,9 +5139,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="1" max="1" width="50" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -4466,10 +5162,10 @@
         <v>37</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>41</v>
@@ -4477,79 +5173,655 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>108</v>
+        <v>54</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>144</v>
+        <v>55</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D2" s="3">
-        <v>37</v>
+        <v>100</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>146</v>
+        <v>57</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>147</v>
+        <v>58</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>148</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>233</v>
+        <v>72</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>240</v>
+        <v>87</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3" s="3">
-        <v>17</v>
+        <v>88</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>242</v>
+        <v>89</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>243</v>
+        <v>90</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>148</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="3">
+        <v>71</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="3">
+        <v>71</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="3">
+        <v>47</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="3">
+        <v>40</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="3">
+        <v>37</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="3">
+        <v>36</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="3">
+        <v>36</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="3">
+        <v>32</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="3">
+        <v>28</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="3">
+        <v>28</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="3">
+        <v>27</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="3">
+        <v>24</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" s="3">
+        <v>24</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="3">
+        <v>23</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="3">
+        <v>23</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="3">
+        <v>22</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" s="3">
+        <v>20</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D21" s="3">
+        <v>20</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D22" s="3">
+        <v>20</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B23" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="3">
+      <c r="C23" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D23" s="3">
+        <v>12</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24" s="3">
+        <v>12</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D25" s="3">
+        <v>10</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D26" s="3">
+        <v>10</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D27" s="3">
         <v>3</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>148</v>
+      <c r="E27" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D28" s="3">
+        <v>3</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4"/>
+  <autoFilter ref="A1:G28"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
     <hyperlink ref="F4" r:id="rId3"/>
+    <hyperlink ref="F5" r:id="rId4"/>
+    <hyperlink ref="F6" r:id="rId5"/>
+    <hyperlink ref="F7" r:id="rId6"/>
+    <hyperlink ref="F8" r:id="rId7"/>
+    <hyperlink ref="F9" r:id="rId8"/>
+    <hyperlink ref="F10" r:id="rId9"/>
+    <hyperlink ref="F11" r:id="rId10"/>
+    <hyperlink ref="F12" r:id="rId11"/>
+    <hyperlink ref="F13" r:id="rId12"/>
+    <hyperlink ref="F14" r:id="rId13"/>
+    <hyperlink ref="F15" r:id="rId14"/>
+    <hyperlink ref="F16" r:id="rId15"/>
+    <hyperlink ref="F17" r:id="rId16"/>
+    <hyperlink ref="F18" r:id="rId17"/>
+    <hyperlink ref="F19" r:id="rId18"/>
+    <hyperlink ref="F20" r:id="rId19"/>
+    <hyperlink ref="F21" r:id="rId20"/>
+    <hyperlink ref="F22" r:id="rId21"/>
+    <hyperlink ref="F23" r:id="rId22"/>
+    <hyperlink ref="F24" r:id="rId23"/>
+    <hyperlink ref="F25" r:id="rId24"/>
+    <hyperlink ref="F26" r:id="rId25"/>
+    <hyperlink ref="F27" r:id="rId26"/>
+    <hyperlink ref="F28" r:id="rId27"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4564,178 +5836,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>322</v>
+        <v>375</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>323</v>
+        <v>376</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>324</v>
+        <v>377</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>304</v>
+        <v>355</v>
       </c>
       <c r="B2" s="3">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>325</v>
+        <v>378</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="B3" s="3">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>326</v>
+        <v>379</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="B4" s="3">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>328</v>
+        <v>380</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>289</v>
+        <v>316</v>
       </c>
       <c r="B5" s="3">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>330</v>
+        <v>382</v>
       </c>
       <c r="B6" s="3">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>331</v>
+        <v>383</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>332</v>
+        <v>384</v>
       </c>
       <c r="B7" s="3">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>333</v>
+        <v>385</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>250</v>
+        <v>365</v>
       </c>
       <c r="B8" s="3">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>334</v>
+        <v>386</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>335</v>
+        <v>295</v>
       </c>
       <c r="B9" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>336</v>
+        <v>387</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>308</v>
+        <v>388</v>
       </c>
       <c r="B10" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>337</v>
+        <v>389</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>338</v>
+        <v>390</v>
       </c>
       <c r="B11" s="3">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>339</v>
+        <v>391</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="B12" s="3">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>341</v>
+        <v>392</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>295</v>
+        <v>393</v>
       </c>
       <c r="B13" s="3">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>342</v>
+        <v>394</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>343</v>
+        <v>395</v>
       </c>
       <c r="B14" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>344</v>
+        <v>396</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>345</v>
+        <v>397</v>
       </c>
       <c r="B15" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>346</v>
+        <v>398</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>347</v>
+        <v>399</v>
       </c>
       <c r="B16" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>348</v>
+        <v>400</v>
       </c>
     </row>
   </sheetData>
@@ -4755,10 +6027,10 @@
         <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>349</v>
+        <v>401</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>350</v>
+        <v>402</v>
       </c>
     </row>
     <row r="2">
@@ -4766,10 +6038,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>351</v>
+        <v>403</v>
       </c>
     </row>
     <row r="3">
@@ -4777,10 +6049,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>352</v>
+        <v>404</v>
       </c>
     </row>
     <row r="4">
@@ -4788,10 +6060,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>353</v>
+        <v>405</v>
       </c>
     </row>
     <row r="5">
@@ -4802,7 +6074,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>354</v>
+        <v>406</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +6095,13 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>355</v>
+        <v>407</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>356</v>
+        <v>408</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>357</v>
+        <v>409</v>
       </c>
     </row>
     <row r="2">
@@ -4837,10 +6109,10 @@
         <v>31</v>
       </c>
       <c r="B2" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>358</v>
+        <v>410</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -4849,22 +6121,22 @@
         <v>30</v>
       </c>
       <c r="B3" s="3">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>358</v>
+        <v>410</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>359</v>
+        <v>411</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>358</v>
+        <v>410</v>
       </c>
       <c r="D4" s="3"/>
     </row>
